--- a/InputData/elec/MLfPPR/Min Life for Pwr Plnt Rtmnts.xlsx
+++ b/InputData/elec/MLfPPR/Min Life for Pwr Plnt Rtmnts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\MLfPPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-india\InputData\elec\MLfPPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA7C5469-9B83-49E8-84E0-DAD6D1CD82B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ADDDD2-9A7E-40B9-A700-6C21CCB17CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27720" yWindow="3885" windowWidth="28770" windowHeight="17370" xr2:uid="{67B50A2A-83E2-40E1-A966-DC033ADD8EBF}"/>
+    <workbookView xWindow="13500" yWindow="945" windowWidth="15270" windowHeight="10725" activeTab="1" xr2:uid="{2912233B-254F-4042-9A53-35B016354AA5}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,38 +37,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>MLfPPR Minimum Lifetime for Power Plant Retirements</t>
   </si>
   <si>
-    <t xml:space="preserve">Sources: </t>
-  </si>
-  <si>
-    <t>(none)</t>
-  </si>
-  <si>
-    <t>This is a calibrated parameter to prevent plants younger than a certain age from retiring economically.</t>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>Ministry of Power</t>
+  </si>
+  <si>
+    <t>https://sansad.in/getFile/annex/268/AU2876_8WpWCz.pdf?source=pqars#:~:text=(a):%20The%20average%20operational,techno%2Deconomic%20and%20environmental%20considerations.</t>
+  </si>
+  <si>
+    <t>certain age from retiring economically.</t>
   </si>
   <si>
     <t>Lifetime</t>
   </si>
   <si>
-    <t>All Plants</t>
-  </si>
-  <si>
     <t>All years</t>
+  </si>
+  <si>
+    <t>All plants</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This is a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>calibrated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parameter to prevent plants younger than a </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">For India, CERC also contains data on "Useful Life" of different </t>
+  </si>
+  <si>
+    <t>power plants (https://www.cercind.gov.in/2020/regulation/159_SoR.pdf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which can be used synonymously to "Minimum Life". Need to revisit </t>
+  </si>
+  <si>
+    <t>during calibration</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -73,7 +115,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -95,14 +151,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -129,39 +202,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -213,7 +286,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -324,13 +397,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -339,6 +405,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -403,37 +476,136 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B7A547-DAFD-4CBC-90C6-A86A1413C282}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4617622-18D4-4412-B0DA-B0E502E28412}">
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="6"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" location=":~:text=(a):%20The%20average%20operational,techno%2Deconomic%20and%20environmental%20considerations." xr:uid="{C86A3946-62E2-4E12-9B4E-FE405B2C61B4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4905432-9D5F-4233-97FF-22F0CC03D67D}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -441,31 +613,196 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498B6747-53CF-4C1D-84DD-4D89524F3F28}">
-  <sheetPr>
-    <tabColor rgb="FF002060"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2918bd8377d530163f38b9d795b11f91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="78da601b2f01cef83512fa5499e996db" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEBEC664-FFCC-467B-9C41-0A059FA5A618}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EA84457-74E1-4C2A-A184-5E92D201D666}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4021AB5-8FDD-498F-9D64-C12624A12E78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>